--- a/printing/regression/training_error_results/20250905training_error_results_0.6_0.9.xlsx
+++ b/printing/regression/training_error_results/20250905training_error_results_0.6_0.9.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cchih\Desktop\NTHU\MasterThesis\GA\SGM_GA\printing\regression\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cchih\Desktop\NTHU\MasterThesis\GA\SGM_GA\printing\regression\training_error_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E168382D-8B95-4D80-8128-34DCFC032C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61F5AA9-5ACB-46B9-9993-262619B4A722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30600" yWindow="1440" windowWidth="27000" windowHeight="14040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Training_Error_Details" sheetId="1" r:id="rId1"/>
@@ -149,7 +149,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.0000"/>
+    <numFmt numFmtId="176" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -212,7 +212,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1388,6 +1388,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="B1" s="1" t="s">
